--- a/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T3_0.xlsx
+++ b/data/controles_results/dif_medias/controls_staggered_vars/difmedias_controles_staggered_variables_2018_T3_0.xlsx
@@ -45,7 +45,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>88</t>
+    <t>84</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -57,40 +57,40 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>0.284</t>
+    <t>0.298</t>
+  </si>
+  <si>
+    <t>(0.050)</t>
+  </si>
+  <si>
+    <t>0.488</t>
+  </si>
+  <si>
+    <t>(0.055)</t>
+  </si>
+  <si>
+    <t>0.262</t>
   </si>
   <si>
     <t>(0.048)</t>
   </si>
   <si>
-    <t>0.466</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>0.250</t>
-  </si>
-  <si>
-    <t>(0.046)</t>
-  </si>
-  <si>
-    <t>0.841</t>
-  </si>
-  <si>
-    <t>(0.245)</t>
-  </si>
-  <si>
-    <t>1.193</t>
-  </si>
-  <si>
-    <t>(0.209)</t>
-  </si>
-  <si>
-    <t>0.375</t>
-  </si>
-  <si>
-    <t>(0.088)</t>
+    <t>0.881</t>
+  </si>
+  <si>
+    <t>(0.256)</t>
+  </si>
+  <si>
+    <t>1.250</t>
+  </si>
+  <si>
+    <t>(0.217)</t>
+  </si>
+  <si>
+    <t>0.393</t>
+  </si>
+  <si>
+    <t>(0.091)</t>
   </si>
   <si>
     <t>26</t>
@@ -138,7 +138,7 @@
     <t>(0.228)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -150,22 +150,22 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>0.254**</t>
-  </si>
-  <si>
-    <t>0.380***</t>
-  </si>
-  <si>
-    <t>0.481***</t>
-  </si>
-  <si>
-    <t>1.274</t>
-  </si>
-  <si>
-    <t>2.230***</t>
-  </si>
-  <si>
-    <t>0.971***</t>
+    <t>0.241**</t>
+  </si>
+  <si>
+    <t>0.358***</t>
+  </si>
+  <si>
+    <t>0.469***</t>
+  </si>
+  <si>
+    <t>1.234</t>
+  </si>
+  <si>
+    <t>2.173***</t>
+  </si>
+  <si>
+    <t>0.953***</t>
   </si>
 </sst>
 </file>
